--- a/tests/test-chase-credit-01.xlsx
+++ b/tests/test-chase-credit-01.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Chase3093_Activity20220626_20220703_20220801" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Chase9999_Activity20111111_20221222_20330830" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -83,6 +83,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
